--- a/data/WP17/WP17_auswertung_parteien.xlsx
+++ b/data/WP17/WP17_auswertung_parteien.xlsx
@@ -389,16 +389,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="C2" t="n">
-        <v>31.0427978281699</v>
+        <v>31.0401913875598</v>
       </c>
       <c r="D2" t="n">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="E2" t="n">
-        <v>40.2361199744735</v>
+        <v>40.1913875598086</v>
       </c>
     </row>
     <row r="3">
@@ -409,13 +409,13 @@
         <v>1689</v>
       </c>
       <c r="C3" t="n">
-        <v>31.3932384341637</v>
+        <v>31.3801065719361</v>
       </c>
       <c r="D3" t="n">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E3" t="n">
-        <v>38.1290704558911</v>
+        <v>38.0106571936057</v>
       </c>
     </row>
     <row r="4">
@@ -423,16 +423,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C4" t="n">
-        <v>31.7619387027798</v>
+        <v>31.7482219061166</v>
       </c>
       <c r="D4" t="n">
         <v>869</v>
       </c>
       <c r="E4" t="n">
-        <v>38.1494661921708</v>
+        <v>38.1934566145092</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +443,7 @@
         <v>291</v>
       </c>
       <c r="C5" t="n">
-        <v>29.651724137931</v>
+        <v>29.6288659793814</v>
       </c>
       <c r="D5" t="n">
         <v>152</v>
@@ -686,13 +686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC916E4E-1D62-4490-9601-2621F6AA9123}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA9DF2B-CDED-4746-9E42-9065ADE8EF98}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D1119B5-2F2F-4C1F-8693-FD3648991428}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA624E7E-21CD-4398-9D26-060CA5D86391}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10B8ED70-7A6D-4220-9485-7E0690E2E24D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E26BFFA-9817-4228-933D-4A2A66338AAE}"/>
 </file>
--- a/data/WP17/WP17_auswertung_parteien.xlsx
+++ b/data/WP17/WP17_auswertung_parteien.xlsx
@@ -392,13 +392,13 @@
         <v>3135</v>
       </c>
       <c r="C2" t="n">
-        <v>31.0401913875598</v>
+        <v>30.8239234449761</v>
       </c>
       <c r="D2" t="n">
-        <v>1875</v>
+        <v>1861</v>
       </c>
       <c r="E2" t="n">
-        <v>40.1913875598086</v>
+        <v>40.6379585326954</v>
       </c>
     </row>
     <row r="3">
@@ -409,13 +409,13 @@
         <v>1689</v>
       </c>
       <c r="C3" t="n">
-        <v>31.3801065719361</v>
+        <v>31.9721728833629</v>
       </c>
       <c r="D3" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E3" t="n">
-        <v>38.0106571936057</v>
+        <v>38.0698638247484</v>
       </c>
     </row>
     <row r="4">
@@ -426,13 +426,13 @@
         <v>1406</v>
       </c>
       <c r="C4" t="n">
-        <v>31.7482219061166</v>
+        <v>31.126600284495</v>
       </c>
       <c r="D4" t="n">
-        <v>869</v>
+        <v>839</v>
       </c>
       <c r="E4" t="n">
-        <v>38.1934566145092</v>
+        <v>40.3271692745377</v>
       </c>
     </row>
     <row r="5">
@@ -443,13 +443,13 @@
         <v>291</v>
       </c>
       <c r="C5" t="n">
-        <v>29.6288659793814</v>
+        <v>29.6666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E5" t="n">
-        <v>47.766323024055</v>
+        <v>47.0790378006873</v>
       </c>
     </row>
   </sheetData>
@@ -686,13 +686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA9DF2B-CDED-4746-9E42-9065ADE8EF98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03AED823-3B70-4E6B-AC56-2F10A11FB4EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA624E7E-21CD-4398-9D26-060CA5D86391}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C9E4ADF-E263-4A22-9FA6-F907BC5589C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E26BFFA-9817-4228-933D-4A2A66338AAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CCA79B6-C6D3-4904-B557-9C031C4237D0}"/>
 </file>
--- a/data/WP17/WP17_auswertung_parteien.xlsx
+++ b/data/WP17/WP17_auswertung_parteien.xlsx
@@ -395,10 +395,10 @@
         <v>30.8239234449761</v>
       </c>
       <c r="D2" t="n">
-        <v>1861</v>
+        <v>2104</v>
       </c>
       <c r="E2" t="n">
-        <v>40.6379585326954</v>
+        <v>32.8867623604466</v>
       </c>
     </row>
     <row r="3">
@@ -412,10 +412,10 @@
         <v>31.9721728833629</v>
       </c>
       <c r="D3" t="n">
-        <v>1046</v>
+        <v>1144</v>
       </c>
       <c r="E3" t="n">
-        <v>38.0698638247484</v>
+        <v>32.267613972765</v>
       </c>
     </row>
     <row r="4">
@@ -429,10 +429,10 @@
         <v>31.126600284495</v>
       </c>
       <c r="D4" t="n">
-        <v>839</v>
+        <v>923</v>
       </c>
       <c r="E4" t="n">
-        <v>40.3271692745377</v>
+        <v>34.352773826458</v>
       </c>
     </row>
     <row r="5">
@@ -446,10 +446,10 @@
         <v>29.6666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E5" t="n">
-        <v>47.0790378006873</v>
+        <v>40.893470790378</v>
       </c>
     </row>
   </sheetData>
@@ -686,13 +686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03AED823-3B70-4E6B-AC56-2F10A11FB4EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56917F6-CC15-4FA4-BF09-64C018BBE304}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C9E4ADF-E263-4A22-9FA6-F907BC5589C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9C8AC33-2AE9-4CFA-8227-1D6571A356F4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CCA79B6-C6D3-4904-B557-9C031C4237D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8453AB-0F44-4D4B-B6ED-98269E7F31BB}"/>
 </file>